--- a/exports/trend_1d/SENSEX_full_report.xlsx
+++ b/exports/trend_1d/SENSEX_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:U102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>28717.91</v>
+        <v>28227.39</v>
       </c>
       <c r="I2" t="n">
         <v>28513.17057860519</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>2.29</v>
+        <v>0.54</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="N2" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O2" t="n">
         <v>2.66</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>4.77</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42065</v>
+        <v>42066</v>
       </c>
       <c r="H3" t="n">
-        <v>29459.14</v>
+        <v>29593.73</v>
       </c>
       <c r="I3" t="n">
         <v>29573.05886762479</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.36</v>
+        <v>-4.84</v>
       </c>
       <c r="L3" t="n">
-        <v>4.78</v>
+        <v>4.99</v>
       </c>
       <c r="M3" t="n">
         <v>0.65</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>4.21</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H4" t="n">
-        <v>28469.67</v>
+        <v>28261.08</v>
       </c>
       <c r="I4" t="n">
         <v>28399.48789495226</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.8</v>
+        <v>-4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>4.09</v>
+        <v>4.68</v>
       </c>
       <c r="M4" t="n">
         <v>0.45</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>4.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42101</v>
+        <v>42102</v>
       </c>
       <c r="H5" t="n">
-        <v>28516.59</v>
+        <v>28707.75</v>
       </c>
       <c r="I5" t="n">
         <v>28667.15647609973</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9</v>
+        <v>-1.58</v>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="M5" t="n">
         <v>0.72</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>4.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H6" t="n">
-        <v>28442.1</v>
+        <v>27886.21</v>
       </c>
       <c r="I6" t="n">
         <v>27953.4291442323</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.93</v>
+        <v>-2.86</v>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.84</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
         <v>0.67</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.08</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42145</v>
+        <v>42146</v>
       </c>
       <c r="H7" t="n">
-        <v>27809.35</v>
+        <v>27957.5</v>
       </c>
       <c r="I7" t="n">
         <v>27938.84798583485</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" t="n">
-        <v>0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="L7" t="n">
         <v>2.34</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>4.03</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42157</v>
+        <v>42158</v>
       </c>
       <c r="H8" t="n">
-        <v>27188.38</v>
+        <v>26837.2</v>
       </c>
       <c r="I8" t="n">
         <v>26845.59854067709</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.75</v>
+        <v>-4.01</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="M8" t="n">
         <v>0.31</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>4.99</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H9" t="n">
-        <v>27316.17</v>
+        <v>27730.21</v>
       </c>
       <c r="I9" t="n">
         <v>27529.9882706539</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.78</v>
+        <v>-3.33</v>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>3.52</v>
       </c>
       <c r="M9" t="n">
         <v>0.48</v>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="O9" t="n">
         <v>-1.29</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.48</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H10" t="n">
-        <v>28112.31</v>
+        <v>27561.38</v>
       </c>
       <c r="I10" t="n">
         <v>27616.13488960853</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" t="n">
-        <v>1.38</v>
+        <v>-0.61</v>
       </c>
       <c r="L10" t="n">
         <v>1.88</v>
@@ -1011,7 +1130,7 @@
         <v>1.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="O10" t="n">
         <v>1.52</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.63</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H11" t="n">
-        <v>26220.95</v>
+        <v>26785.55</v>
       </c>
       <c r="I11" t="n">
         <v>26689.60018321782</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>4.86</v>
+        <v>2.81</v>
       </c>
       <c r="L11" t="n">
         <v>3.11</v>
@@ -1068,7 +1199,7 @@
         <v>1.64</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>-1.96</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42311</v>
+        <v>42312</v>
       </c>
       <c r="H12" t="n">
-        <v>26590.59</v>
+        <v>26552.92</v>
       </c>
       <c r="I12" t="n">
         <v>26553.72226638352</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.73</v>
+        <v>-0.87</v>
       </c>
       <c r="L12" t="n">
         <v>1.53</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>3.85</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42362</v>
+        <v>42366</v>
       </c>
       <c r="H13" t="n">
-        <v>25838.71</v>
+        <v>26034.13</v>
       </c>
       <c r="I13" t="n">
         <v>25891.0805674685</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K13" t="n">
-        <v>2.69</v>
+        <v>1.95</v>
       </c>
       <c r="L13" t="n">
         <v>0.93</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>3.49</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H14" t="n">
-        <v>25406.33</v>
+        <v>24851.83</v>
       </c>
       <c r="I14" t="n">
         <v>25363.47766030494</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.41</v>
+        <v>-4.54</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>4.64</v>
       </c>
       <c r="M14" t="n">
-        <v>0.17</v>
+        <v>0.71</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
         <v>0.76</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>4.4</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H15" t="n">
-        <v>23779.35</v>
+        <v>24242.98</v>
       </c>
       <c r="I15" t="n">
         <v>24187.16868517243</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" t="n">
-        <v>4.32</v>
+        <v>2.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
         <v>3.38</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.12</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H16" t="n">
-        <v>28292.81</v>
+        <v>27827.53</v>
       </c>
       <c r="I16" t="n">
         <v>28197.80968524384</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K16" t="n">
-        <v>16.71</v>
+        <v>14.79</v>
       </c>
       <c r="L16" t="n">
         <v>0.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4.33</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H17" t="n">
-        <v>26633.13</v>
+        <v>26878.24</v>
       </c>
       <c r="I17" t="n">
         <v>26673.31037635116</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K17" t="n">
-        <v>4.29</v>
+        <v>3.41</v>
       </c>
       <c r="L17" t="n">
         <v>2.34</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.1</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H18" t="n">
-        <v>32014.19</v>
+        <v>31797.84</v>
       </c>
       <c r="I18" t="n">
         <v>31830.25554511768</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K18" t="n">
-        <v>19.11</v>
+        <v>18.3</v>
       </c>
       <c r="L18" t="n">
         <v>0.66</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>2.64</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42989</v>
+        <v>42990</v>
       </c>
       <c r="H19" t="n">
-        <v>31882.16</v>
+        <v>32158.66</v>
       </c>
       <c r="I19" t="n">
         <v>32114.94032420181</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.27</v>
+        <v>-1.13</v>
       </c>
       <c r="L19" t="n">
-        <v>0.53</v>
+        <v>1.18</v>
       </c>
       <c r="M19" t="n">
         <v>0.51</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>2.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H20" t="n">
-        <v>31922.44</v>
+        <v>31626.63</v>
       </c>
       <c r="I20" t="n">
         <v>31774.38576473185</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.73</v>
+        <v>-1.65</v>
       </c>
       <c r="L20" t="n">
-        <v>0.85</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
         <v>0.11</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>3.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="H21" t="n">
-        <v>31833.99</v>
+        <v>32182.22</v>
       </c>
       <c r="I21" t="n">
         <v>32156.33547508514</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.66</v>
+        <v>-1.76</v>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7</v>
+        <v>1.09</v>
       </c>
       <c r="O21" t="n">
         <v>-0.93</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.21</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43053</v>
+        <v>43054</v>
       </c>
       <c r="H22" t="n">
-        <v>32941.87</v>
+        <v>32760.44</v>
       </c>
       <c r="I22" t="n">
         <v>32940.45399207708</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.15</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>2.85</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43063</v>
+        <v>43066</v>
       </c>
       <c r="H23" t="n">
-        <v>33679.24</v>
+        <v>33724.44</v>
       </c>
       <c r="I23" t="n">
         <v>33694.36960339591</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.8</v>
+        <v>-2.94</v>
       </c>
       <c r="L23" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="M23" t="n">
         <v>0.85</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>2.54</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43069</v>
+        <v>43070</v>
       </c>
       <c r="H24" t="n">
-        <v>33149.35</v>
+        <v>32832.94</v>
       </c>
       <c r="I24" t="n">
         <v>32916.77619614748</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.71</v>
+        <v>-2.64</v>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
         <v>0.18</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>3.33</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43084</v>
+        <v>43087</v>
       </c>
       <c r="H25" t="n">
-        <v>33462.97</v>
+        <v>33601.68</v>
       </c>
       <c r="I25" t="n">
         <v>33508.27205157319</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.92</v>
+        <v>-2.34</v>
       </c>
       <c r="L25" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
         <v>0.63</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.86</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H26" t="n">
-        <v>35906.66</v>
+        <v>35066.75</v>
       </c>
       <c r="I26" t="n">
         <v>35314.28629710119</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K26" t="n">
-        <v>6.86</v>
+        <v>4.36</v>
       </c>
       <c r="L26" t="n">
         <v>2.99</v>
       </c>
       <c r="M26" t="n">
-        <v>0.29</v>
+        <v>0.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0.72</v>
+        <v>2.34</v>
       </c>
       <c r="O26" t="n">
         <v>0.41</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.36</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H27" t="n">
-        <v>33788.54</v>
+        <v>33880.25</v>
       </c>
       <c r="I27" t="n">
         <v>33798.33115476047</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="L27" t="n">
         <v>1.91</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.14</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H28" t="n">
-        <v>34848.3</v>
+        <v>34616.13</v>
       </c>
       <c r="I28" t="n">
         <v>34827.26352272237</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>2.86</v>
+        <v>2.17</v>
       </c>
       <c r="L28" t="n">
         <v>0.38</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>3.31</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43257</v>
+        <v>43258</v>
       </c>
       <c r="H29" t="n">
-        <v>35178.88</v>
+        <v>35463.08</v>
       </c>
       <c r="I29" t="n">
         <v>35442.3531062159</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.63</v>
+        <v>-2.45</v>
       </c>
       <c r="L29" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="M29" t="n">
         <v>0.78</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.06</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H30" t="n">
-        <v>38389.82</v>
+        <v>37922.17</v>
       </c>
       <c r="I30" t="n">
         <v>37955.2402136362</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K30" t="n">
-        <v>8.25</v>
+        <v>6.93</v>
       </c>
       <c r="L30" t="n">
         <v>1.48</v>
@@ -2151,7 +2510,7 @@
         <v>0.46</v>
       </c>
       <c r="N30" t="n">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="O30" t="n">
         <v>0.8100000000000001</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>3.46</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43419</v>
+        <v>43420</v>
       </c>
       <c r="H31" t="n">
-        <v>35260.54</v>
+        <v>35457.16</v>
       </c>
       <c r="I31" t="n">
         <v>35321.1977231715</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K31" t="n">
-        <v>7.02</v>
+        <v>6.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.14</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>3.93</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H32" t="n">
-        <v>35673.25</v>
+        <v>34959.72</v>
       </c>
       <c r="I32" t="n">
         <v>35052.29595170297</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>0.61</v>
+        <v>-1.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.58</v>
       </c>
       <c r="M32" t="n">
-        <v>0.53</v>
+        <v>1.31</v>
       </c>
       <c r="N32" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>0.5600000000000001</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>4.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43448</v>
+        <v>43451</v>
       </c>
       <c r="H33" t="n">
-        <v>35962.93</v>
+        <v>36270.07</v>
       </c>
       <c r="I33" t="n">
         <v>36257.09656400103</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.87</v>
+        <v>-3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>3.25</v>
+        <v>3.87</v>
       </c>
       <c r="M33" t="n">
         <v>0.6899999999999999</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>3.81</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H34" t="n">
-        <v>35876.22</v>
+        <v>35808.95</v>
       </c>
       <c r="I34" t="n">
         <v>35853.2582085473</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.09</v>
+        <v>-1.27</v>
       </c>
       <c r="L34" t="n">
         <v>3.47</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>3.19</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H35" t="n">
-        <v>36671.43</v>
+        <v>37054.1</v>
       </c>
       <c r="I35" t="n">
         <v>36758.33767177185</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.41</v>
+        <v>-3.48</v>
       </c>
       <c r="L35" t="n">
-        <v>2.85</v>
+        <v>3.62</v>
       </c>
       <c r="M35" t="n">
         <v>0.6</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>3.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H36" t="n">
-        <v>38276.63</v>
+        <v>37789.13</v>
       </c>
       <c r="I36" t="n">
         <v>38208.86423928407</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K36" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="L36" t="n">
         <v>0.88</v>
@@ -2493,7 +2924,7 @@
         <v>0.63</v>
       </c>
       <c r="N36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O36" t="n">
         <v>1.04</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>3.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H37" t="n">
-        <v>37930.77</v>
+        <v>39352.67</v>
       </c>
       <c r="I37" t="n">
         <v>38572.16078989628</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.37</v>
+        <v>-4.14</v>
       </c>
       <c r="L37" t="n">
-        <v>1.22</v>
+        <v>4.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0.59</v>
+        <v>2.03</v>
       </c>
       <c r="N37" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="O37" t="n">
         <v>-1.27</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.27</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H38" t="n">
-        <v>39513.39</v>
+        <v>38720.57</v>
       </c>
       <c r="I38" t="n">
         <v>38789.79792063365</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>0.41</v>
+        <v>-1.61</v>
       </c>
       <c r="L38" t="n">
         <v>1.99</v>
@@ -2607,7 +3062,7 @@
         <v>0.19</v>
       </c>
       <c r="N38" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="O38" t="n">
         <v>3.75</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H39" t="n">
-        <v>36093.47</v>
+        <v>38014.62</v>
       </c>
       <c r="I39" t="n">
         <v>37732.31983975548</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K39" t="n">
-        <v>6.78</v>
+        <v>1.82</v>
       </c>
       <c r="L39" t="n">
         <v>1.95</v>
@@ -2664,7 +3131,7 @@
         <v>1.81</v>
       </c>
       <c r="N39" t="n">
-        <v>2.16</v>
+        <v>5.32</v>
       </c>
       <c r="O39" t="n">
         <v>-2.01</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.26</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H40" t="n">
-        <v>41464.61</v>
+        <v>40676.63</v>
       </c>
       <c r="I40" t="n">
         <v>40714.49858129347</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K40" t="n">
-        <v>9.08</v>
+        <v>7</v>
       </c>
       <c r="L40" t="n">
         <v>5.07</v>
@@ -2721,7 +3200,7 @@
         <v>0.44</v>
       </c>
       <c r="N40" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="O40" t="n">
         <v>5.32</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>3.57</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43840</v>
+        <v>43843</v>
       </c>
       <c r="H41" t="n">
-        <v>41599.72</v>
+        <v>41859.69</v>
       </c>
       <c r="I41" t="n">
         <v>41855.94514689266</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.27</v>
+        <v>-2.91</v>
       </c>
       <c r="L41" t="n">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="M41" t="n">
         <v>0.98</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>2.99</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H42" t="n">
-        <v>40913.82</v>
+        <v>40723.49</v>
       </c>
       <c r="I42" t="n">
         <v>40909.77315131669</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.26</v>
+        <v>-2.71</v>
       </c>
       <c r="L42" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="M42" t="n">
         <v>0.25</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>3.56</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43866</v>
+        <v>43867</v>
       </c>
       <c r="H43" t="n">
-        <v>41142.66</v>
+        <v>41306.03</v>
       </c>
       <c r="I43" t="n">
         <v>41288.67922612876</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.03</v>
+        <v>-1.43</v>
       </c>
       <c r="L43" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
         <v>0.77</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>3.84</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H44" t="n">
-        <v>40281.2</v>
+        <v>39888.96</v>
       </c>
       <c r="I44" t="n">
         <v>40123.04802188715</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.48</v>
+        <v>-3.43</v>
       </c>
       <c r="L44" t="n">
-        <v>2.63</v>
+        <v>3.74</v>
       </c>
       <c r="M44" t="n">
         <v>0.32</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>3.86</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H45" t="n">
-        <v>32720.16</v>
+        <v>33717.62</v>
       </c>
       <c r="I45" t="n">
         <v>32836.20850490947</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K45" t="n">
-        <v>17.97</v>
+        <v>15.47</v>
       </c>
       <c r="L45" t="n">
         <v>0.92</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H46" t="n">
-        <v>31097.73</v>
+        <v>30028.98</v>
       </c>
       <c r="I46" t="n">
         <v>30355.17723416471</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.77</v>
+        <v>-10.94</v>
       </c>
       <c r="L46" t="n">
-        <v>8.74</v>
+        <v>11.12</v>
       </c>
       <c r="M46" t="n">
         <v>2.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>11.8</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H47" t="n">
-        <v>32424.1</v>
+        <v>33303.52</v>
       </c>
       <c r="I47" t="n">
         <v>33293.01558381879</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.98</v>
+        <v>-10.9</v>
       </c>
       <c r="L47" t="n">
-        <v>8.16</v>
+        <v>12.14</v>
       </c>
       <c r="M47" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="N47" t="n">
         <v>3.25</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.88</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H48" t="n">
-        <v>38845.82</v>
+        <v>38034.14</v>
       </c>
       <c r="I48" t="n">
         <v>38098.48511275087</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K48" t="n">
-        <v>16.64</v>
+        <v>14.2</v>
       </c>
       <c r="L48" t="n">
         <v>2.87</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.41</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44105</v>
+        <v>44109</v>
       </c>
       <c r="H49" t="n">
-        <v>38697.05</v>
+        <v>38973.7</v>
       </c>
       <c r="I49" t="n">
         <v>38827.4406781054</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.74</v>
+        <v>-2.47</v>
       </c>
       <c r="L49" t="n">
-        <v>2.52</v>
+        <v>3.23</v>
       </c>
       <c r="M49" t="n">
         <v>1.2</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.58</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H50" t="n">
-        <v>48347.59</v>
+        <v>47409.93</v>
       </c>
       <c r="I50" t="n">
         <v>47848.26329380894</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K50" t="n">
-        <v>24.05</v>
+        <v>21.65</v>
       </c>
       <c r="L50" t="n">
         <v>0.39</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>5.57</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44228</v>
+        <v>44229</v>
       </c>
       <c r="H51" t="n">
-        <v>48600.61</v>
+        <v>49797.72</v>
       </c>
       <c r="I51" t="n">
         <v>49114.26310643195</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.51</v>
+        <v>-5.04</v>
       </c>
       <c r="L51" t="n">
-        <v>2.86</v>
+        <v>5.79</v>
       </c>
       <c r="M51" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="N51" t="n">
         <v>5</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.47</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H52" t="n">
-        <v>50889.76</v>
+        <v>49744.32</v>
       </c>
       <c r="I52" t="n">
         <v>49840.69119710854</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>2.19</v>
+        <v>-0.11</v>
       </c>
       <c r="L52" t="n">
         <v>1.21</v>
@@ -3405,7 +4028,7 @@
         <v>0.28</v>
       </c>
       <c r="N52" t="n">
-        <v>0.85</v>
+        <v>2.25</v>
       </c>
       <c r="O52" t="n">
         <v>2.46</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.06</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H53" t="n">
-        <v>49564.86</v>
+        <v>50540.48</v>
       </c>
       <c r="I53" t="n">
         <v>50463.46429684143</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K53" t="n">
-        <v>0.36</v>
+        <v>-1.6</v>
       </c>
       <c r="L53" t="n">
         <v>4.18</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.8</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H54" t="n">
-        <v>61143.33</v>
+        <v>59984.7</v>
       </c>
       <c r="I54" t="n">
         <v>60026.63373770555</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K54" t="n">
-        <v>20.98</v>
+        <v>18.69</v>
       </c>
       <c r="L54" t="n">
         <v>1.4</v>
@@ -3519,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>1.1</v>
+        <v>1.89</v>
       </c>
       <c r="O54" t="n">
         <v>1.97</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.66</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H55" t="n">
-        <v>58253.82</v>
+        <v>59183.22</v>
       </c>
       <c r="I55" t="n">
         <v>58697.25652076265</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K55" t="n">
-        <v>2.89</v>
+        <v>1.34</v>
       </c>
       <c r="L55" t="n">
         <v>1.83</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.66</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H56" t="n">
-        <v>59464.62</v>
+        <v>59037.18</v>
       </c>
       <c r="I56" t="n">
         <v>59321.46594681429</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
-        <v>0.48</v>
+        <v>-0.25</v>
       </c>
       <c r="L56" t="n">
         <v>1.48</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>3.61</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H57" t="n">
-        <v>55776.85</v>
+        <v>56816.65</v>
       </c>
       <c r="I57" t="n">
         <v>56686.49002439689</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K57" t="n">
-        <v>5.52</v>
+        <v>3.76</v>
       </c>
       <c r="L57" t="n">
         <v>0.98</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.91</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44664</v>
+        <v>44669</v>
       </c>
       <c r="H58" t="n">
-        <v>58338.93</v>
+        <v>57166.74</v>
       </c>
       <c r="I58" t="n">
         <v>57558.1859554222</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K58" t="n">
-        <v>2.68</v>
+        <v>0.62</v>
       </c>
       <c r="L58" t="n">
         <v>0.75</v>
       </c>
       <c r="M58" t="n">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="N58" t="n">
-        <v>0.99</v>
+        <v>2.01</v>
       </c>
       <c r="O58" t="n">
         <v>1.86</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.6</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H59" t="n">
-        <v>53750.97</v>
+        <v>54178.46</v>
       </c>
       <c r="I59" t="n">
         <v>54075.10437654286</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K59" t="n">
-        <v>5.98</v>
+        <v>5.23</v>
       </c>
       <c r="L59" t="n">
         <v>1.44</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>4.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H60" t="n">
-        <v>58833.87</v>
+        <v>57972.62</v>
       </c>
       <c r="I60" t="n">
         <v>58393.91108910495</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K60" t="n">
-        <v>8.59</v>
+        <v>7</v>
       </c>
       <c r="L60" t="n">
         <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>0.97</v>
+        <v>2.49</v>
       </c>
       <c r="N60" t="n">
         <v>1.46</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>3.55</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44813</v>
+        <v>44816</v>
       </c>
       <c r="H61" t="n">
-        <v>59793.14</v>
+        <v>60115.13</v>
       </c>
       <c r="I61" t="n">
         <v>60033.25050546698</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.14</v>
+        <v>-3.7</v>
       </c>
       <c r="L61" t="n">
-        <v>3.7</v>
+        <v>3.99</v>
       </c>
       <c r="M61" t="n">
         <v>0.6</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>3.47</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H62" t="n">
-        <v>59119.72</v>
+        <v>58098.92</v>
       </c>
       <c r="I62" t="n">
         <v>58491.36168840415</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.66</v>
+        <v>-3.35</v>
       </c>
       <c r="L62" t="n">
-        <v>2.71</v>
+        <v>3.55</v>
       </c>
       <c r="M62" t="n">
         <v>1.91</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.94</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H63" t="n">
-        <v>59107.19</v>
+        <v>59202.9</v>
       </c>
       <c r="I63" t="n">
         <v>59185.81195085443</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.74</v>
+        <v>-1.9</v>
       </c>
       <c r="L63" t="n">
         <v>2.24</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.12</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H64" t="n">
-        <v>61799.03</v>
+        <v>61337.81</v>
       </c>
       <c r="I64" t="n">
         <v>61686.52871878675</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K64" t="n">
-        <v>4.39</v>
+        <v>3.61</v>
       </c>
       <c r="L64" t="n">
         <v>0.7</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H65" t="n">
-        <v>61275.09</v>
+        <v>61319.51</v>
       </c>
       <c r="I65" t="n">
         <v>61295.57509964982</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="L65" t="n">
         <v>1.09</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>2.93</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>44980</v>
+        <v>44981</v>
       </c>
       <c r="H66" t="n">
-        <v>59605.8</v>
+        <v>59463.93</v>
       </c>
       <c r="I66" t="n">
         <v>59522.34405131305</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.79</v>
+        <v>-3.03</v>
       </c>
       <c r="L66" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="M66" t="n">
         <v>0.53</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>3.44</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H67" t="n">
-        <v>59689.31</v>
+        <v>59832.97</v>
       </c>
       <c r="I67" t="n">
         <v>59704.50727183718</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.38</v>
+        <v>-0.62</v>
       </c>
       <c r="L67" t="n">
         <v>1.74</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>3.4</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H68" t="n">
-        <v>65782.78</v>
+        <v>65240.68</v>
       </c>
       <c r="I68" t="n">
         <v>65588.06322526238</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K68" t="n">
-        <v>9.94</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L68" t="n">
         <v>0.7</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>3.12</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H69" t="n">
-        <v>66265.56</v>
+        <v>66598.91</v>
       </c>
       <c r="I69" t="n">
         <v>66457.00634183525</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.57</v>
+        <v>-2.08</v>
       </c>
       <c r="L69" t="n">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="M69" t="n">
         <v>0.44</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>2.28</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45189</v>
+        <v>45190</v>
       </c>
       <c r="H70" t="n">
-        <v>66800.84</v>
+        <v>66230.24000000001</v>
       </c>
       <c r="I70" t="n">
         <v>66305.16404599458</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K70" t="n">
-        <v>0.3</v>
+        <v>-0.55</v>
       </c>
       <c r="L70" t="n">
-        <v>0.45</v>
+        <v>0.71</v>
       </c>
       <c r="M70" t="n">
         <v>0.76</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>2.59</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H71" t="n">
-        <v>64933.87</v>
+        <v>65675.92999999999</v>
       </c>
       <c r="I71" t="n">
         <v>65265.26387753303</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K71" t="n">
-        <v>1.96</v>
+        <v>0.84</v>
       </c>
       <c r="L71" t="n">
         <v>0.57</v>
       </c>
       <c r="M71" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="O71" t="n">
         <v>-0.85</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>2.6</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="H72" t="n">
-        <v>71500.75999999999</v>
+        <v>71186.86</v>
       </c>
       <c r="I72" t="n">
         <v>71229.85134336905</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K72" t="n">
-        <v>8.869999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L72" t="n">
         <v>0.46</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>3.05</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="H73" t="n">
-        <v>72500.3</v>
+        <v>73745.35000000001</v>
       </c>
       <c r="I73" t="n">
         <v>73244.92381365862</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.85</v>
+        <v>-3.59</v>
       </c>
       <c r="L73" t="n">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="M73" t="n">
         <v>0.84</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,25 +5525,25 @@
         <v>3.96</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H74" t="n">
-        <v>72748.42</v>
+        <v>72012.05</v>
       </c>
       <c r="I74" t="n">
         <v>72130.73102508753</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.35</v>
+        <v>-2.35</v>
       </c>
       <c r="L74" t="n">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="M74" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="N74" t="n">
         <v>1.23</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>3.39</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="H75" t="n">
-        <v>74248.22</v>
+        <v>74742.5</v>
       </c>
       <c r="I75" t="n">
         <v>74271.40822361618</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>-3.11</v>
+        <v>-3.79</v>
       </c>
       <c r="L75" t="n">
-        <v>3.46</v>
+        <v>3.97</v>
       </c>
       <c r="M75" t="n">
         <v>0.73</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>2.94</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="H76" t="n">
-        <v>73399.78</v>
+        <v>72943.67999999999</v>
       </c>
       <c r="I76" t="n">
         <v>72992.63724905087</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.8</v>
+        <v>-2.41</v>
       </c>
       <c r="L76" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="M76" t="n">
         <v>1.25</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>2.84</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45434</v>
+        <v>45435</v>
       </c>
       <c r="H77" t="n">
-        <v>74221.06</v>
+        <v>75418.03999999999</v>
       </c>
       <c r="I77" t="n">
         <v>74826.92489186913</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>-1.75</v>
+        <v>-3.39</v>
       </c>
       <c r="L77" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="M77" t="n">
         <v>0.79</v>
       </c>
       <c r="N77" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="O77" t="n">
         <v>-0.62</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>3.75</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H78" t="n">
-        <v>76468.78</v>
+        <v>72079.05</v>
       </c>
       <c r="I78" t="n">
         <v>73442.97901142284</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K78" t="n">
-        <v>1.39</v>
+        <v>-4.43</v>
       </c>
       <c r="L78" t="n">
-        <v>2.32</v>
+        <v>6.87</v>
       </c>
       <c r="M78" t="n">
         <v>0.46</v>
       </c>
       <c r="N78" t="n">
-        <v>0.89</v>
+        <v>5.74</v>
       </c>
       <c r="O78" t="n">
         <v>1.61</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>7.7</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45467</v>
+        <v>45468</v>
       </c>
       <c r="H79" t="n">
-        <v>77341.08</v>
+        <v>78053.52</v>
       </c>
       <c r="I79" t="n">
         <v>77626.86288971946</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.3</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>8.01</v>
+        <v>8.44</v>
       </c>
       <c r="M79" t="n">
         <v>1.32</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>3.98</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H80" t="n">
-        <v>80981.95</v>
+        <v>78759.39999999999</v>
       </c>
       <c r="I80" t="n">
         <v>79647.88892820536</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K80" t="n">
-        <v>3.75</v>
+        <v>0.9</v>
       </c>
       <c r="L80" t="n">
         <v>0.76</v>
       </c>
       <c r="M80" t="n">
-        <v>0.87</v>
+        <v>2.96</v>
       </c>
       <c r="N80" t="n">
-        <v>1.08</v>
+        <v>2.74</v>
       </c>
       <c r="O80" t="n">
         <v>0.92</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>4.05</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H81" t="n">
-        <v>81785.56</v>
+        <v>82134.61</v>
       </c>
       <c r="I81" t="n">
         <v>81790.19945087626</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.84</v>
+        <v>-4.29</v>
       </c>
       <c r="L81" t="n">
-        <v>4.16</v>
+        <v>4.48</v>
       </c>
       <c r="M81" t="n">
         <v>1.39</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>2.57</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H82" t="n">
-        <v>84266.28999999999</v>
+        <v>82497.10000000001</v>
       </c>
       <c r="I82" t="n">
         <v>83712.60216210794</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K82" t="n">
-        <v>2.6</v>
+        <v>0.44</v>
       </c>
       <c r="L82" t="n">
         <v>1.51</v>
       </c>
       <c r="M82" t="n">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
       <c r="N82" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="O82" t="n">
         <v>0.43</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>3.74</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H83" t="n">
-        <v>80004.06</v>
+        <v>80234.08</v>
       </c>
       <c r="I83" t="n">
         <v>80179.15744660067</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K83" t="n">
-        <v>3.02</v>
+        <v>2.74</v>
       </c>
       <c r="L83" t="n">
         <v>1.52</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>3.91</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H84" t="n">
-        <v>79218.05</v>
+        <v>78041.59</v>
       </c>
       <c r="I84" t="n">
         <v>79119.6613414399</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K84" t="n">
-        <v>-1.27</v>
+        <v>-2.73</v>
       </c>
       <c r="L84" t="n">
-        <v>1.64</v>
+        <v>2.94</v>
       </c>
       <c r="M84" t="n">
         <v>1.44</v>
       </c>
       <c r="N84" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O84" t="n">
         <v>0.29</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>4.8</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H85" t="n">
-        <v>77186.74000000001</v>
+        <v>78583.81</v>
       </c>
       <c r="I85" t="n">
         <v>78178.78269517834</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K85" t="n">
-        <v>1.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L85" t="n">
         <v>2.6</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>4.14</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="H86" t="n">
-        <v>75939.17999999999</v>
+        <v>75735.96000000001</v>
       </c>
       <c r="I86" t="n">
         <v>75891.78891312155</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K86" t="n">
-        <v>-3.37</v>
+        <v>-3.62</v>
       </c>
       <c r="L86" t="n">
         <v>4.19</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>3.07</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H87" t="n">
-        <v>74169.95</v>
+        <v>75301.25999999999</v>
       </c>
       <c r="I87" t="n">
         <v>75134.36499583954</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K87" t="n">
-        <v>2.07</v>
+        <v>0.57</v>
       </c>
       <c r="L87" t="n">
         <v>0.08</v>
@@ -5400,7 +6443,7 @@
         <v>0.78</v>
       </c>
       <c r="N87" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="O87" t="n">
         <v>-0.27</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,19 +6491,19 @@
         <v>3.59</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H88" t="n">
-        <v>76295.36</v>
+        <v>75364.69</v>
       </c>
       <c r="I88" t="n">
         <v>75720.01447148064</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K88" t="n">
-        <v>1.32</v>
+        <v>0.08</v>
       </c>
       <c r="L88" t="n">
         <v>1.09</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -5493,28 +6560,28 @@
         <v>4</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H89" t="n">
-        <v>75157.25999999999</v>
+        <v>76734.89</v>
       </c>
       <c r="I89" t="n">
         <v>75966.42570944122</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>0.28</v>
+        <v>-1.82</v>
       </c>
       <c r="L89" t="n">
-        <v>1.19</v>
+        <v>2.05</v>
       </c>
       <c r="M89" t="n">
-        <v>1.34</v>
+        <v>2.26</v>
       </c>
       <c r="N89" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="O89" t="n">
         <v>-1.22</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S89" t="b">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5550,19 +6629,19 @@
         <v>5.04</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H90" t="n">
-        <v>82184.17</v>
+        <v>81463.09</v>
       </c>
       <c r="I90" t="n">
         <v>81699.41964057604</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K90" t="n">
-        <v>7.1</v>
+        <v>6.16</v>
       </c>
       <c r="L90" t="n">
         <v>0.39</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+      <c r="U90" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -5607,22 +6698,22 @@
         <v>2.66</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H91" t="n">
-        <v>81785.74000000001</v>
+        <v>82380.69</v>
       </c>
       <c r="I91" t="n">
         <v>82001.49616267963</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.4</v>
+        <v>-1.13</v>
       </c>
       <c r="L91" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="M91" t="n">
         <v>1.1</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S91" t="b">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>3</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -5664,28 +6767,28 @@
         <v>2.4</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H92" t="n">
-        <v>81715.63</v>
+        <v>81159.67999999999</v>
       </c>
       <c r="I92" t="n">
         <v>81309.15790495498</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.48</v>
       </c>
       <c r="L92" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="M92" t="n">
         <v>0.58</v>
       </c>
       <c r="N92" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="O92" t="n">
         <v>0.73</v>
@@ -5694,7 +6797,19 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S92" t="b">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5721,22 +6836,22 @@
         <v>2.47</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H93" t="n">
-        <v>82172.10000000001</v>
+        <v>82500.82000000001</v>
       </c>
       <c r="I93" t="n">
         <v>82183.01036343805</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K93" t="n">
-        <v>-1.25</v>
+        <v>-1.65</v>
       </c>
       <c r="L93" t="n">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="M93" t="n">
         <v>0.22</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -5778,19 +6905,19 @@
         <v>2.37</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H94" t="n">
-        <v>84180.96000000001</v>
+        <v>83576.24000000001</v>
       </c>
       <c r="I94" t="n">
         <v>83912.71306137035</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K94" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="L94" t="n">
         <v>0.87</v>
@@ -5808,7 +6935,19 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>4</v>
+      </c>
+      <c r="U94" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -5835,19 +6974,19 @@
         <v>2.63</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H95" t="n">
-        <v>84065.75</v>
+        <v>84273.92</v>
       </c>
       <c r="I95" t="n">
         <v>84150.32493648332</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="L95" t="n">
         <v>2.75</v>
@@ -5865,7 +7004,19 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S95" t="b">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
+        <v>2</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5892,25 +7043,25 @@
         <v>3.84</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H96" t="n">
-        <v>81287.19</v>
+        <v>80238.85000000001</v>
       </c>
       <c r="I96" t="n">
         <v>81250.00142852028</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K96" t="n">
-        <v>-3.54</v>
+        <v>-4.79</v>
       </c>
       <c r="L96" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="M96" t="n">
-        <v>0.92</v>
+        <v>3.38</v>
       </c>
       <c r="N96" t="n">
         <v>1.48</v>
@@ -5922,7 +7073,19 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S96" t="b">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -5949,28 +7112,28 @@
         <v>3.46</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H97" t="n">
-        <v>74616.58</v>
+        <v>77562.89999999999</v>
       </c>
       <c r="I97" t="n">
         <v>77181.25788017771</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K97" t="n">
-        <v>7.01</v>
+        <v>3.33</v>
       </c>
       <c r="L97" t="n">
         <v>0.49</v>
       </c>
       <c r="M97" t="n">
-        <v>2.52</v>
+        <v>3.58</v>
       </c>
       <c r="N97" t="n">
-        <v>1.89</v>
+        <v>3.95</v>
       </c>
       <c r="O97" t="n">
         <v>-1.29</v>
@@ -5979,7 +7142,19 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S97" t="b">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>2</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6006,28 +7181,28 @@
         <v>7.08</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H98" t="n">
-        <v>76015.28</v>
+        <v>74559.24000000001</v>
       </c>
       <c r="I98" t="n">
         <v>74882.60304479852</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K98" t="n">
-        <v>-2</v>
+        <v>-3.87</v>
       </c>
       <c r="L98" t="n">
-        <v>2.18</v>
+        <v>4.01</v>
       </c>
       <c r="M98" t="n">
         <v>2.08</v>
       </c>
       <c r="N98" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="O98" t="n">
         <v>3.95</v>
@@ -6036,7 +7211,19 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S98" t="b">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>2</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -6063,22 +7250,22 @@
         <v>5.25</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H99" t="n">
-        <v>76264.33</v>
+        <v>76808.48</v>
       </c>
       <c r="I99" t="n">
         <v>76530.01736598423</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K99" t="n">
-        <v>-2.29</v>
+        <v>-3.02</v>
       </c>
       <c r="L99" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="M99" t="n">
         <v>1.59</v>
@@ -6093,7 +7280,19 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S99" t="b">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>2</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -6120,19 +7319,19 @@
         <v>4.04</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H100" t="n">
-        <v>76944.28</v>
+        <v>76570.35000000001</v>
       </c>
       <c r="I100" t="n">
         <v>76654.84901113676</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K100" t="n">
-        <v>0.18</v>
+        <v>-0.31</v>
       </c>
       <c r="L100" t="n">
         <v>1.74</v>
@@ -6150,7 +7349,19 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S100" t="b">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>4</v>
+      </c>
+      <c r="U100" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -6177,19 +7388,19 @@
         <v>2.02</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H101" t="n">
-        <v>72781.89</v>
+        <v>74315.61</v>
       </c>
       <c r="I101" t="n">
         <v>74246.84415171549</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K101" t="n">
-        <v>4.95</v>
+        <v>2.94</v>
       </c>
       <c r="L101" t="n">
         <v>0.46</v>
@@ -6198,7 +7409,7 @@
         <v>0.79</v>
       </c>
       <c r="N101" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="O101" t="n">
         <v>-0.49</v>
@@ -6207,7 +7418,19 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R101" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S101" t="b">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>2</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6258,6 +7481,14 @@
       <c r="Q102" t="n">
         <v>9</v>
       </c>
+      <c r="R102" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S102" t="b">
+        <v>1</v>
+      </c>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11216,7 +12447,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.2</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="6">
@@ -11226,7 +12457,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="7">
@@ -11236,7 +12467,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -11246,7 +12477,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -11256,7 +12487,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="10">
@@ -11266,7 +12497,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90.2</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -11276,7 +12507,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -11286,7 +12517,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -11296,7 +12527,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -11306,7 +12537,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.68</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="15">
@@ -11316,7 +12547,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.91</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="16">
@@ -11326,7 +12557,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.45</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="17">
@@ -11336,7 +12567,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.05</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="18">
@@ -11346,7 +12577,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -11356,7 +12587,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="20">
@@ -11366,7 +12597,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="21">
@@ -11376,7 +12607,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.74</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="22">
@@ -11386,7 +12617,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -11396,7 +12627,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -11406,7 +12637,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="25">
@@ -11426,7 +12657,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="27">
@@ -11446,7 +12677,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
